--- a/batch/sharepoint/staff_schedules/staff_schedule_450601_20260810.xlsx
+++ b/batch/sharepoint/staff_schedules/staff_schedule_450601_20260810.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R33"/>
+  <dimension ref="A1:S58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,25 +508,30 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>Overtime</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>Called Out</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Floated In</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>Census</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -550,7 +555,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>08/10/2026</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -565,17 +570,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>STF004947</t>
+          <t>STF006211</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Smith, Brittany</t>
+          <t>Zuniga, Sandra</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -587,26 +592,23 @@
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M6" t="n">
-        <v>12</v>
-      </c>
-      <c r="N6" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>7</v>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>orientee paired</t>
-        </is>
-      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="n">
+        <v>7</v>
+      </c>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -641,17 +643,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>STF004948</t>
+          <t>STF006077</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Jensen, Richard</t>
+          <t>Montgomery, Gabriella</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -663,18 +665,23 @@
         <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M7" t="n">
-        <v>12</v>
-      </c>
-      <c r="N7" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="n">
-        <v>7</v>
-      </c>
-      <c r="R7" t="inlineStr">
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="n">
+        <v>7</v>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>float pool</t>
         </is>
@@ -703,27 +710,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>STF004956</t>
+          <t>STF006121</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Gross, Brett</t>
+          <t>Foster, Daniel</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -735,18 +742,31 @@
         <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M8" t="n">
         <v>12</v>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="n">
-        <v>7</v>
-      </c>
-      <c r="R8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R8" t="n">
+        <v>7</v>
+      </c>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -771,27 +791,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>STF004926</t>
+          <t>STF006079</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Johnson, Teresa</t>
+          <t>Johnson, Erica</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -803,22 +823,27 @@
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="n">
-        <v>7</v>
-      </c>
-      <c r="R9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="n">
+        <v>7</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>agency</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -838,55 +863,64 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>STF004930</t>
+          <t>STF006056</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Gay, Joshua</t>
+          <t>Bryant, Hailey</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
-        <v>12</v>
-      </c>
-      <c r="N10" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
-        <v>7</v>
-      </c>
-      <c r="R10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="n">
+        <v>7</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>orientee paired</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -906,32 +940,32 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>08/10/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>STF004937</t>
+          <t>STF006142</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Reed, Angela</t>
+          <t>Delgado, Susan</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -943,18 +977,31 @@
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
         <v>12</v>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
-        <v>7</v>
-      </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="n">
+        <v>7</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>orientee paired</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -974,12 +1021,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>OC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -994,17 +1041,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>STF004926</t>
+          <t>STF006135</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Johnson, Teresa</t>
+          <t>Flores, Brenda</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>LPN</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1016,19 +1063,20 @@
       <c r="M12" t="n">
         <v>12</v>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>7</v>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>orientee paired</t>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>7</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>agency</t>
         </is>
       </c>
     </row>
@@ -1050,12 +1098,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>OC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1070,12 +1118,12 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>STF004935</t>
+          <t>STF006089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Miller, John</t>
+          <t>Curtis, Desiree</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1084,7 +1132,7 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L13" t="n">
         <v>12</v>
@@ -1092,15 +1140,20 @@
       <c r="M13" t="n">
         <v>12</v>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="n">
-        <v>7</v>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>orientee paired</t>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="n">
+        <v>7</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>double shift</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1175,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1137,17 +1190,17 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>STF004930</t>
+          <t>STF006047</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Gay, Joshua</t>
+          <t>Cardenas, Cheryl</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1156,25 +1209,26 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L14" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>12</v>
-      </c>
-      <c r="N14" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="n">
-        <v>7</v>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>agency</t>
-        </is>
-      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="n">
+        <v>7</v>
+      </c>
+      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1194,7 +1248,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1209,44 +1263,45 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>STF004948</t>
+          <t>STF006142</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Jensen, Richard</t>
+          <t>Delgado, Susan</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>LPN</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M15" t="n">
-        <v>12</v>
-      </c>
-      <c r="N15" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="n">
-        <v>7</v>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>float pool</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="n">
+        <v>7</v>
+      </c>
+      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1266,32 +1321,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>08/12/2026</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>STF004929</t>
+          <t>STF006072</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Johnson, Tyler</t>
+          <t>Johnson, Jesus</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1303,18 +1358,23 @@
         <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M16" t="n">
-        <v>12</v>
-      </c>
-      <c r="N16" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
-        <v>7</v>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="n">
+        <v>7</v>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>float pool</t>
         </is>
@@ -1338,32 +1398,32 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>STF004956</t>
+          <t>STF006156</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Gross, Brett</t>
+          <t>Krueger, Kelly</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1375,22 +1435,23 @@
         <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M17" t="n">
-        <v>12</v>
-      </c>
-      <c r="N17" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="n">
-        <v>7</v>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>agency</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="n">
+        <v>7</v>
+      </c>
+      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1410,32 +1471,32 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>STF004935</t>
+          <t>STF006049</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Miller, John</t>
+          <t>Jackson, Margaret</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1444,21 +1505,26 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L18" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M18" t="n">
-        <v>12</v>
-      </c>
-      <c r="N18" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="n">
-        <v>7</v>
-      </c>
-      <c r="R18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="n">
+        <v>7</v>
+      </c>
+      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1478,32 +1544,32 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>STF004956</t>
+          <t>STF006044</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Gross, Brett</t>
+          <t>Hernandez, Sonya</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1515,18 +1581,27 @@
         <v>1</v>
       </c>
       <c r="L19" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M19" t="n">
-        <v>12</v>
-      </c>
-      <c r="N19" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="n">
-        <v>7</v>
-      </c>
-      <c r="R19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="n">
+        <v>7</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>float pool</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1546,12 +1621,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>OC</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1566,17 +1641,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>STF004936</t>
+          <t>STF006070</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Chambers, Emily</t>
+          <t>Martinez, Mark</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>LPN</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1586,15 +1661,24 @@
         <v>12</v>
       </c>
       <c r="M20" t="n">
-        <v>12</v>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+        <v>14</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="n">
+        <v>7</v>
+      </c>
+      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1614,12 +1698,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>08/11/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>OC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1634,17 +1718,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>STF004926</t>
+          <t>STF006135</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Johnson, Teresa</t>
+          <t>Flores, Brenda</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>LPN</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1656,15 +1740,20 @@
       <c r="M21" t="n">
         <v>12</v>
       </c>
-      <c r="N21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="n">
-        <v>7</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>float pool</t>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="n">
+        <v>7</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>agency</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1775,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1701,42 +1790,47 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>STF004930</t>
+          <t>STF006160</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Gay, Joshua</t>
+          <t>Bell, Carlos</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>NP</t>
         </is>
       </c>
       <c r="K22" t="n">
         <v>1</v>
       </c>
       <c r="L22" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M22" t="n">
-        <v>12</v>
-      </c>
-      <c r="N22" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="n">
-        <v>7</v>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>orientee paired</t>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="n">
+        <v>7</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>float pool</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1852,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1773,40 +1867,49 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>STF004931</t>
+          <t>STF006078</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Dudley, Roy</t>
+          <t>Curry, Melissa</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>RN</t>
         </is>
       </c>
       <c r="K23" t="n">
         <v>1</v>
       </c>
       <c r="L23" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M23" t="n">
-        <v>12</v>
-      </c>
-      <c r="N23" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="n">
-        <v>7</v>
-      </c>
-      <c r="R23" t="inlineStr"/>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="n">
+        <v>7</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>double shift</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1826,32 +1929,32 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>STF004944</t>
+          <t>STF006211</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Hale, Melissa</t>
+          <t>Zuniga, Sandra</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1863,18 +1966,23 @@
         <v>1</v>
       </c>
       <c r="L24" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M24" t="n">
-        <v>12</v>
-      </c>
-      <c r="N24" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="n">
-        <v>7</v>
-      </c>
-      <c r="R24" t="inlineStr"/>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="n">
+        <v>7</v>
+      </c>
+      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1894,32 +2002,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>STF004921</t>
+          <t>STF006121</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Cooper, Christopher</t>
+          <t>Foster, Daniel</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1931,22 +2039,23 @@
         <v>1</v>
       </c>
       <c r="L25" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M25" t="n">
-        <v>12</v>
-      </c>
-      <c r="N25" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>7</v>
-      </c>
-      <c r="R25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="n">
+        <v>7</v>
+      </c>
+      <c r="S25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1966,55 +2075,60 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>STF004953</t>
+          <t>STF006097</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Mitchell, Jesus</t>
+          <t>Henson, Melissa</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>LPN</t>
         </is>
       </c>
       <c r="K26" t="n">
         <v>1</v>
       </c>
       <c r="L26" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M26" t="n">
-        <v>12</v>
-      </c>
-      <c r="N26" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="n">
-        <v>7</v>
-      </c>
-      <c r="R26" t="inlineStr"/>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="n">
+        <v>7</v>
+      </c>
+      <c r="S26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2034,32 +2148,32 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>N</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>STF004944</t>
+          <t>STF006081</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Hale, Melissa</t>
+          <t>Wells, Karen</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2071,18 +2185,23 @@
         <v>1</v>
       </c>
       <c r="L27" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M27" t="n">
-        <v>12</v>
-      </c>
-      <c r="N27" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
-        <v>7</v>
-      </c>
-      <c r="R27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="n">
+        <v>7</v>
+      </c>
+      <c r="S27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2102,12 +2221,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>OC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2122,12 +2241,12 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>STF004930</t>
+          <t>STF006114</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Gay, Joshua</t>
+          <t>George, Melissa</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2144,17 +2263,22 @@
       <c r="M28" t="n">
         <v>12</v>
       </c>
-      <c r="N28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>7</v>
-      </c>
-      <c r="R28" t="inlineStr"/>
+      <c r="P28" t="inlineStr"/>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="n">
+        <v>7</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>float pool</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2174,61 +2298,62 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>D</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>STF004956</t>
+          <t>STF006097</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Gross, Brett</t>
+          <t>Henson, Melissa</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>LPN</t>
         </is>
       </c>
       <c r="K29" t="n">
         <v>1</v>
       </c>
       <c r="L29" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M29" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="n">
-        <v>7</v>
-      </c>
-      <c r="R29" t="inlineStr">
-        <is>
-          <t>float pool</t>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="n">
+        <v>7</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>orientee paired</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2375,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>08/13/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2265,44 +2390,45 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>STF004935</t>
+          <t>STF006166</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Miller, John</t>
+          <t>Fox, Aaron</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>RN</t>
+          <t>LPN</t>
         </is>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
       <c r="L30" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M30" t="n">
-        <v>12</v>
-      </c>
-      <c r="N30" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
-        <v>7</v>
-      </c>
-      <c r="R30" t="inlineStr">
-        <is>
-          <t>agency</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="n">
+        <v>7</v>
+      </c>
+      <c r="S30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2322,55 +2448,60 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>08/13/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>STF004931</t>
+          <t>STF006070</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Dudley, Roy</t>
+          <t>Martinez, Mark</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>LPN</t>
         </is>
       </c>
       <c r="K31" t="n">
         <v>1</v>
       </c>
       <c r="L31" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M31" t="n">
-        <v>12</v>
-      </c>
-      <c r="N31" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="n">
-        <v>7</v>
-      </c>
-      <c r="R31" t="inlineStr">
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="n">
+        <v>7</v>
+      </c>
+      <c r="S31" t="inlineStr">
         <is>
           <t>agency</t>
         </is>
@@ -2394,55 +2525,60 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>E</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>STF004931</t>
+          <t>STF006136</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Dudley, Roy</t>
+          <t>Small, Kyle</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>NP</t>
+          <t>LPN</t>
         </is>
       </c>
       <c r="K32" t="n">
         <v>1</v>
       </c>
       <c r="L32" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M32" t="n">
-        <v>12</v>
-      </c>
-      <c r="N32" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="n">
-        <v>7</v>
-      </c>
-      <c r="R32" t="inlineStr"/>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="n">
+        <v>7</v>
+      </c>
+      <c r="S32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2462,7 +2598,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2472,7 +2608,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -2482,12 +2618,12 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>STF004926</t>
+          <t>STF006042</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Johnson, Teresa</t>
+          <t>Juarez, Timothy</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2499,18 +2635,1863 @@
         <v>1</v>
       </c>
       <c r="L33" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="M33" t="n">
-        <v>12</v>
-      </c>
-      <c r="N33" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="n">
-        <v>7</v>
-      </c>
-      <c r="R33" t="inlineStr"/>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="n">
+        <v>7</v>
+      </c>
+      <c r="S33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>STF006114</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>George, Melissa</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K34" t="n">
+        <v>1</v>
+      </c>
+      <c r="L34" t="n">
+        <v>8</v>
+      </c>
+      <c r="M34" t="n">
+        <v>8</v>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="n">
+        <v>7</v>
+      </c>
+      <c r="S34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>STF006106</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Maldonado, Morgan</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>1</v>
+      </c>
+      <c r="L35" t="n">
+        <v>12</v>
+      </c>
+      <c r="M35" t="n">
+        <v>12</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="n">
+        <v>7</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>08/14/2026</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>STF006089</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Curtis, Desiree</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K36" t="n">
+        <v>2</v>
+      </c>
+      <c r="L36" t="n">
+        <v>8</v>
+      </c>
+      <c r="M36" t="n">
+        <v>8</v>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="n">
+        <v>7</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>double shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>STF006211</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Zuniga, Sandra</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>1</v>
+      </c>
+      <c r="L37" t="n">
+        <v>8</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>absent</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="n">
+        <v>7</v>
+      </c>
+      <c r="S37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>STF006077</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Montgomery, Gabriella</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
+        <v>1</v>
+      </c>
+      <c r="L38" t="n">
+        <v>8</v>
+      </c>
+      <c r="M38" t="n">
+        <v>8</v>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr"/>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="n">
+        <v>7</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>STF006084</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Taylor, Bruce</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>8</v>
+      </c>
+      <c r="M39" t="n">
+        <v>8</v>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>completed</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="n">
+        <v>7</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>STF006081</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Wells, Karen</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>1</v>
+      </c>
+      <c r="L40" t="n">
+        <v>8</v>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="n">
+        <v>7</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>double shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>STF006139</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Hernandez, Noah</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>1</v>
+      </c>
+      <c r="L41" t="n">
+        <v>8</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr"/>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="n">
+        <v>7</v>
+      </c>
+      <c r="S41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>STF006152</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Nolan, Seth</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K42" t="n">
+        <v>1</v>
+      </c>
+      <c r="L42" t="n">
+        <v>12</v>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="n">
+        <v>7</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>double shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>STF006166</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Fox, Aaron</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>LPN</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>1</v>
+      </c>
+      <c r="L43" t="n">
+        <v>8</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="n">
+        <v>7</v>
+      </c>
+      <c r="S43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>08/15/2026</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>STF006049</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Jackson, Margaret</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K44" t="n">
+        <v>2</v>
+      </c>
+      <c r="L44" t="n">
+        <v>8</v>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="n">
+        <v>7</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>double shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>STF006139</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Hernandez, Noah</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>1</v>
+      </c>
+      <c r="L45" t="n">
+        <v>8</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr"/>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="n">
+        <v>7</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>double shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>STF006121</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Foster, Daniel</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>1</v>
+      </c>
+      <c r="L46" t="n">
+        <v>8</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="n">
+        <v>7</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>double shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>STF006048</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Pollard, Joseph</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>1</v>
+      </c>
+      <c r="L47" t="n">
+        <v>8</v>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="n">
+        <v>7</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>float pool</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>STF006106</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Maldonado, Morgan</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K48" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" t="n">
+        <v>8</v>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr"/>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="n">
+        <v>7</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>orientee paired</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>STF006078</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Curry, Melissa</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" t="n">
+        <v>12</v>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="n">
+        <v>7</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>orientee paired</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>STF006160</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Bell, Carlos</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>NP</t>
+        </is>
+      </c>
+      <c r="K50" t="n">
+        <v>1</v>
+      </c>
+      <c r="L50" t="n">
+        <v>12</v>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr"/>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>7</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>agency</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>STF006152</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Nolan, Seth</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K51" t="n">
+        <v>1</v>
+      </c>
+      <c r="L51" t="n">
+        <v>8</v>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="n">
+        <v>7</v>
+      </c>
+      <c r="S51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>STF006079</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Johnson, Erica</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>8</v>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr"/>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="n">
+        <v>7</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>double shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>STF006068</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Mendez, Robert</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>1</v>
+      </c>
+      <c r="L53" t="n">
+        <v>8</v>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="n">
+        <v>7</v>
+      </c>
+      <c r="S53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>STF006077</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Montgomery, Gabriella</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K54" t="n">
+        <v>1</v>
+      </c>
+      <c r="L54" t="n">
+        <v>8</v>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="n">
+        <v>7</v>
+      </c>
+      <c r="S54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>STF006047</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Cardenas, Cheryl</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K55" t="n">
+        <v>2</v>
+      </c>
+      <c r="L55" t="n">
+        <v>8</v>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="n">
+        <v>7</v>
+      </c>
+      <c r="S55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>STF006101</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Jenkins, Michael</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K56" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" t="n">
+        <v>8</v>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="n">
+        <v>7</v>
+      </c>
+      <c r="S56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>STF006152</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Nolan, Seth</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K57" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" t="n">
+        <v>12</v>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr"/>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="n">
+        <v>7</v>
+      </c>
+      <c r="S57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>450601</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Emergency Department (ED)</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>ED</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>OC</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>STF006106</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Maldonado, Morgan</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>RN</t>
+        </is>
+      </c>
+      <c r="K58" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" t="n">
+        <v>12</v>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>scheduled</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
+      <c r="Q58" t="inlineStr"/>
+      <c r="R58" t="n">
+        <v>7</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>orientee paired</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
